--- a/survey_templates/011_research_study_participation_permission_form--survey_templates.xlsx
+++ b/survey_templates/011_research_study_participation_permission_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -911,8 +911,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -940,12 +940,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'decline'}</t>
+          <t>decline</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Decline'}</t>
+          <t>Decline</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'lab_1'}</t>
+          <t>lab_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Lab 1'}</t>
+          <t>Lab 1</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'lab_2'}</t>
+          <t>lab_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Lab 2'}</t>
+          <t>Lab 2</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'public'}</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Public'}</t>
+          <t>Public</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'private'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Private'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'within_1-2_years'}</t>
+          <t>within_1-2_years</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Within 1-2 years'}</t>
+          <t>Within 1-2 years</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'within_5_years'}</t>
+          <t>within_5_years</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Within 5 years'}</t>
+          <t>Within 5 years</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'after_5_years'}</t>
+          <t>after_5_years</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'After 5 years'}</t>
+          <t>After 5 years</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'electronic_signature'}</t>
+          <t>electronic_signature</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Electronic Signature'}</t>
+          <t>Electronic Signature</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'physical_signature'}</t>
+          <t>physical_signature</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Physical Signature'}</t>
+          <t>Physical Signature</t>
         </is>
       </c>
     </row>
